--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128720039</v>
+        <v>128719243</v>
       </c>
       <c r="B2" t="n">
-        <v>80195</v>
+        <v>56880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>370595</v>
+        <v>370475</v>
       </c>
       <c r="R2" t="n">
-        <v>6873897</v>
+        <v>6873855</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,12 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växer på sälg vid planerad körväg. Skogen avverkningsanmäld</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,50 +798,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128719243</v>
+        <v>128719294</v>
       </c>
       <c r="B3" t="n">
-        <v>56880</v>
+        <v>75177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,7 +842,7 @@
         <v>6873855</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128719294</v>
+        <v>128740970</v>
       </c>
       <c r="B4" t="n">
-        <v>75177</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,40 +919,53 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hästnäset, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>370475</v>
+        <v>370569</v>
       </c>
       <c r="R4" t="n">
-        <v>6873855</v>
+        <v>6873887</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,22 +989,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128719478</v>
+        <v>128740217</v>
       </c>
       <c r="B5" t="n">
-        <v>75177</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,40 +1042,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hästnäset, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>370439</v>
+        <v>370577</v>
       </c>
       <c r="R5" t="n">
-        <v>6873847</v>
+        <v>6873885</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,22 +1112,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,6 +1151,1191 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128720039</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80195</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hästnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>370595</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6873897</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växer på sälg vid planerad körväg. Skogen avverkningsanmäld</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128741660</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hästnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>370546</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6873884</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128747956</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80195</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hästnäset, Vassbo  Idre, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>370509</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6873867</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128741270</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hästnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>370583</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6873880</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128741066</v>
+      </c>
+      <c r="B10" t="n">
+        <v>75177</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hästnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>370576</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6873882</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128740523</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97462</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hästnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>370572</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6873869</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128719478</v>
+      </c>
+      <c r="B12" t="n">
+        <v>75177</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hästnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>370439</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6873847</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128741523</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hästnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>370557</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6873868</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128740649</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hästnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>370575</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6873870</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128740310</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97462</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hästnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>370572</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6873880</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Lummer innanför Mellanskogs avgränsning. Växer intill ett vattendrag</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128741660</v>
+        <v>128747956</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>80195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,41 +1280,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästnäset, Dlr</t>
+          <t>Hästnäset, Vassbo  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>370546</v>
+        <v>370509</v>
       </c>
       <c r="R7" t="n">
-        <v>6873884</v>
+        <v>6873867</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,8 +1361,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1383,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747956</v>
+        <v>128741660</v>
       </c>
       <c r="B8" t="n">
-        <v>80195</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,37 +1416,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästnäset, Vassbo  Idre, Dlr</t>
+          <t>Hästnäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>370509</v>
+        <v>370546</v>
       </c>
       <c r="R8" t="n">
-        <v>6873867</v>
+        <v>6873884</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1456,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1492,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,34 +1501,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128719478</v>
+        <v>128741523</v>
       </c>
       <c r="B12" t="n">
-        <v>75177</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,21 +1882,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1909,13 +1909,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>370439</v>
+        <v>370557</v>
       </c>
       <c r="R12" t="n">
-        <v>6873847</v>
+        <v>6873868</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1939,22 +1939,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1981,10 +1981,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128741523</v>
+        <v>128719478</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>75177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,21 +1992,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2019,13 +2019,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>370557</v>
+        <v>370439</v>
       </c>
       <c r="R13" t="n">
-        <v>6873868</v>
+        <v>6873847</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2049,22 +2049,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747956</v>
+        <v>128741660</v>
       </c>
       <c r="B7" t="n">
-        <v>80195</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,37 +1280,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästnäset, Vassbo  Idre, Dlr</t>
+          <t>Hästnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>370509</v>
+        <v>370546</v>
       </c>
       <c r="R7" t="n">
-        <v>6873867</v>
+        <v>6873884</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,34 +1365,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1405,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128741660</v>
+        <v>128747956</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>80195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,41 +1394,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästnäset, Dlr</t>
+          <t>Hästnäset, Vassbo  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>370546</v>
+        <v>370509</v>
       </c>
       <c r="R8" t="n">
-        <v>6873884</v>
+        <v>6873867</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1482,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,8 +1475,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128741660</v>
+        <v>128747956</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>80195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,41 +1280,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästnäset, Dlr</t>
+          <t>Hästnäset, Vassbo  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>370546</v>
+        <v>370509</v>
       </c>
       <c r="R7" t="n">
-        <v>6873884</v>
+        <v>6873867</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,8 +1361,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1383,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747956</v>
+        <v>128741660</v>
       </c>
       <c r="B8" t="n">
-        <v>80195</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,37 +1416,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästnäset, Vassbo  Idre, Dlr</t>
+          <t>Hästnäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>370509</v>
+        <v>370546</v>
       </c>
       <c r="R8" t="n">
-        <v>6873867</v>
+        <v>6873884</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1456,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1492,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,34 +1501,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1755,7 +1755,7 @@
         <v>128740523</v>
       </c>
       <c r="B11" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>128740310</v>
       </c>
       <c r="B15" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128719243</v>
       </c>
       <c r="B2" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128719294</v>
       </c>
       <c r="B3" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128740970</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>128740217</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>128720039</v>
       </c>
       <c r="B6" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>128747956</v>
       </c>
       <c r="B7" t="n">
-        <v>80195</v>
+        <v>80222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>128741660</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>128741270</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>128741066</v>
       </c>
       <c r="B10" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128740523</v>
       </c>
       <c r="B11" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>128741523</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>128719478</v>
       </c>
       <c r="B13" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>128740310</v>
       </c>
       <c r="B15" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,7 +801,7 @@
         <v>128719294</v>
       </c>
       <c r="B3" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>128720039</v>
       </c>
       <c r="B6" t="n">
-        <v>80222</v>
+        <v>80226</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747956</v>
+        <v>128741660</v>
       </c>
       <c r="B7" t="n">
-        <v>80222</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,37 +1280,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästnäset, Vassbo  Idre, Dlr</t>
+          <t>Hästnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>370509</v>
+        <v>370546</v>
       </c>
       <c r="R7" t="n">
-        <v>6873867</v>
+        <v>6873884</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,34 +1365,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1405,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128741660</v>
+        <v>128747956</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>80226</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,41 +1394,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästnäset, Dlr</t>
+          <t>Hästnäset, Vassbo  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>370546</v>
+        <v>370509</v>
       </c>
       <c r="R8" t="n">
-        <v>6873884</v>
+        <v>6873867</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1482,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,8 +1475,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1645,7 +1645,7 @@
         <v>128741066</v>
       </c>
       <c r="B10" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128740523</v>
       </c>
       <c r="B11" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>128741523</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>128719478</v>
       </c>
       <c r="B13" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>128740310</v>
       </c>
       <c r="B15" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2336,6 +2336,125 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128875352</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57548</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hästnäset, Vassbo  Idre, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>370551</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6873911</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128741660</v>
+        <v>128747956</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>80226</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,41 +1280,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästnäset, Dlr</t>
+          <t>Hästnäset, Vassbo  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>370546</v>
+        <v>370509</v>
       </c>
       <c r="R7" t="n">
-        <v>6873884</v>
+        <v>6873867</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,8 +1361,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1383,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747956</v>
+        <v>128741660</v>
       </c>
       <c r="B8" t="n">
-        <v>80226</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,37 +1416,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästnäset, Vassbo  Idre, Dlr</t>
+          <t>Hästnäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>370509</v>
+        <v>370546</v>
       </c>
       <c r="R8" t="n">
-        <v>6873867</v>
+        <v>6873884</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1456,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1492,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,34 +1501,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1755,7 +1755,7 @@
         <v>128740523</v>
       </c>
       <c r="B11" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>128740310</v>
       </c>
       <c r="B15" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128719243</v>
       </c>
       <c r="B2" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128719294</v>
       </c>
       <c r="B3" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128740970</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>128740217</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>128720039</v>
       </c>
       <c r="B6" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>128747956</v>
       </c>
       <c r="B7" t="n">
-        <v>80226</v>
+        <v>80230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>128741660</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>128741270</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>128741066</v>
       </c>
       <c r="B10" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128740523</v>
       </c>
       <c r="B11" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>128741523</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>128719478</v>
       </c>
       <c r="B13" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>128740310</v>
       </c>
       <c r="B15" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128875352</v>
       </c>
       <c r="B16" t="n">
-        <v>57548</v>
+        <v>57552</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747956</v>
+        <v>128741660</v>
       </c>
       <c r="B7" t="n">
-        <v>80230</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,37 +1280,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästnäset, Vassbo  Idre, Dlr</t>
+          <t>Hästnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>370509</v>
+        <v>370546</v>
       </c>
       <c r="R7" t="n">
-        <v>6873867</v>
+        <v>6873884</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,34 +1365,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1405,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128741660</v>
+        <v>128747956</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>80230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,41 +1394,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästnäset, Dlr</t>
+          <t>Hästnäset, Vassbo  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>370546</v>
+        <v>370509</v>
       </c>
       <c r="R8" t="n">
-        <v>6873884</v>
+        <v>6873867</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1482,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,8 +1475,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128741523</v>
+        <v>128719478</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>75209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,21 +1882,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1909,13 +1909,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>370557</v>
+        <v>370439</v>
       </c>
       <c r="R12" t="n">
-        <v>6873868</v>
+        <v>6873847</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1939,22 +1939,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1981,10 +1981,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128719478</v>
+        <v>128741523</v>
       </c>
       <c r="B13" t="n">
-        <v>75209</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,21 +1992,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2019,13 +2019,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>370439</v>
+        <v>370557</v>
       </c>
       <c r="R13" t="n">
-        <v>6873847</v>
+        <v>6873868</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2049,22 +2049,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128719243</v>
       </c>
       <c r="B2" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128719294</v>
       </c>
       <c r="B3" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128740970</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>128740217</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>128720039</v>
       </c>
       <c r="B6" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128741660</v>
+        <v>128747956</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>80135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,41 +1280,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästnäset, Dlr</t>
+          <t>Hästnäset, Vassbo  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>370546</v>
+        <v>370509</v>
       </c>
       <c r="R7" t="n">
-        <v>6873884</v>
+        <v>6873867</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,8 +1361,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1383,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747956</v>
+        <v>128741660</v>
       </c>
       <c r="B8" t="n">
-        <v>80230</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,37 +1416,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästnäset, Vassbo  Idre, Dlr</t>
+          <t>Hästnäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>370509</v>
+        <v>370546</v>
       </c>
       <c r="R8" t="n">
-        <v>6873867</v>
+        <v>6873884</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1456,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1492,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,34 +1501,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1522,7 +1522,7 @@
         <v>128741270</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>128741066</v>
       </c>
       <c r="B10" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128740523</v>
       </c>
       <c r="B11" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128719478</v>
+        <v>128741523</v>
       </c>
       <c r="B12" t="n">
-        <v>75209</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1882,21 +1882,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1909,13 +1909,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>370439</v>
+        <v>370557</v>
       </c>
       <c r="R12" t="n">
-        <v>6873847</v>
+        <v>6873868</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1939,22 +1939,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1981,10 +1981,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128741523</v>
+        <v>128719478</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>83005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,21 +1992,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2019,13 +2019,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>370557</v>
+        <v>370439</v>
       </c>
       <c r="R13" t="n">
-        <v>6873868</v>
+        <v>6873847</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2049,22 +2049,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2218,7 +2218,7 @@
         <v>128740310</v>
       </c>
       <c r="B15" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128875352</v>
       </c>
       <c r="B16" t="n">
-        <v>57552</v>
+        <v>57555</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747956</v>
+        <v>128741660</v>
       </c>
       <c r="B7" t="n">
-        <v>80140</v>
+        <v>79034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,37 +1280,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästnäset, Vassbo  Idre, Dlr</t>
+          <t>Hästnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>370509</v>
+        <v>370546</v>
       </c>
       <c r="R7" t="n">
-        <v>6873867</v>
+        <v>6873884</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,34 +1365,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1405,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128741660</v>
+        <v>128747956</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,41 +1394,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästnäset, Dlr</t>
+          <t>Hästnäset, Vassbo  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>370546</v>
+        <v>370509</v>
       </c>
       <c r="R8" t="n">
-        <v>6873884</v>
+        <v>6873867</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1482,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,8 +1475,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1755,7 +1755,7 @@
         <v>128740523</v>
       </c>
       <c r="B11" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>128740310</v>
       </c>
       <c r="B15" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>128719294</v>
       </c>
       <c r="B3" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>128720039</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128741660</v>
+        <v>128747956</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>80141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,41 +1280,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästnäset, Dlr</t>
+          <t>Hästnäset, Vassbo  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>370546</v>
+        <v>370509</v>
       </c>
       <c r="R7" t="n">
-        <v>6873884</v>
+        <v>6873867</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,8 +1361,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1383,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747956</v>
+        <v>128741660</v>
       </c>
       <c r="B8" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,37 +1416,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästnäset, Vassbo  Idre, Dlr</t>
+          <t>Hästnäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>370509</v>
+        <v>370546</v>
       </c>
       <c r="R8" t="n">
-        <v>6873867</v>
+        <v>6873884</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1456,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1492,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,34 +1501,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1645,7 +1645,7 @@
         <v>128741066</v>
       </c>
       <c r="B10" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128740523</v>
       </c>
       <c r="B11" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>128741523</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>128719478</v>
       </c>
       <c r="B13" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>128740310</v>
       </c>
       <c r="B15" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128719243</v>
       </c>
       <c r="B2" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128719294</v>
       </c>
       <c r="B3" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128740970</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>128740217</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>128720039</v>
       </c>
       <c r="B6" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747956</v>
+        <v>128741660</v>
       </c>
       <c r="B7" t="n">
-        <v>80141</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,37 +1280,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästnäset, Vassbo  Idre, Dlr</t>
+          <t>Hästnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>370509</v>
+        <v>370546</v>
       </c>
       <c r="R7" t="n">
-        <v>6873867</v>
+        <v>6873884</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,34 +1365,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1405,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128741660</v>
+        <v>128747956</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>80145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,41 +1394,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästnäset, Dlr</t>
+          <t>Hästnäset, Vassbo  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>370546</v>
+        <v>370509</v>
       </c>
       <c r="R8" t="n">
-        <v>6873884</v>
+        <v>6873867</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1482,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,8 +1475,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1522,7 +1522,7 @@
         <v>128741270</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>128741066</v>
       </c>
       <c r="B10" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128740523</v>
       </c>
       <c r="B11" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>128741523</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>128719478</v>
       </c>
       <c r="B13" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>128740310</v>
       </c>
       <c r="B15" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128875352</v>
       </c>
       <c r="B16" t="n">
-        <v>57555</v>
+        <v>57557</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128741660</v>
+        <v>128747956</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>80145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,41 +1280,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästnäset, Dlr</t>
+          <t>Hästnäset, Vassbo  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>370546</v>
+        <v>370509</v>
       </c>
       <c r="R7" t="n">
-        <v>6873884</v>
+        <v>6873867</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1356,7 +1352,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,8 +1361,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1383,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128747956</v>
+        <v>128741660</v>
       </c>
       <c r="B8" t="n">
-        <v>80145</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,37 +1416,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästnäset, Vassbo  Idre, Dlr</t>
+          <t>Hästnäset, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>370509</v>
+        <v>370546</v>
       </c>
       <c r="R8" t="n">
-        <v>6873867</v>
+        <v>6873884</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1456,7 +1482,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1492,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,34 +1501,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128747956</v>
+        <v>128741660</v>
       </c>
       <c r="B7" t="n">
-        <v>80145</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,37 +1280,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästnäset, Vassbo  Idre, Dlr</t>
+          <t>Hästnäset, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>370509</v>
+        <v>370546</v>
       </c>
       <c r="R7" t="n">
-        <v>6873867</v>
+        <v>6873884</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1342,7 +1346,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,7 +1356,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,34 +1365,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1405,10 +1383,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128741660</v>
+        <v>128747956</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>80145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,41 +1394,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästnäset, Dlr</t>
+          <t>Hästnäset, Vassbo  Idre, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>370546</v>
+        <v>370509</v>
       </c>
       <c r="R8" t="n">
-        <v>6873884</v>
+        <v>6873867</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1482,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1492,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,8 +1475,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128719243</v>
       </c>
       <c r="B2" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>128719294</v>
       </c>
       <c r="B3" t="n">
-        <v>83015</v>
+        <v>83007</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>128740970</v>
       </c>
       <c r="B4" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>128740217</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>128720039</v>
       </c>
       <c r="B6" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>128741660</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>128747956</v>
       </c>
       <c r="B8" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>128741270</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>128741066</v>
       </c>
       <c r="B10" t="n">
-        <v>83015</v>
+        <v>83007</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>128740523</v>
       </c>
       <c r="B11" t="n">
-        <v>97540</v>
+        <v>97549</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>128741523</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>128719478</v>
       </c>
       <c r="B13" t="n">
-        <v>83015</v>
+        <v>83007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>128740310</v>
       </c>
       <c r="B15" t="n">
-        <v>97540</v>
+        <v>97549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128875352</v>
       </c>
       <c r="B16" t="n">
-        <v>57557</v>
+        <v>57559</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 43051-2025 artfynd.xlsx
+++ b/artfynd/A 43051-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128720039</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -923,6 +933,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128747956</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128719374</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1147,6 +1167,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128741523</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128741660</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1380,6 +1410,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128741740</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1494,6 +1529,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128741810</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1608,6 +1648,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128741874</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1722,6 +1767,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128741946</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1836,6 +1886,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128742409</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1946,6 +2001,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128742456</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2056,6 +2116,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128719294</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2166,6 +2231,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128719478</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2276,6 +2346,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128741066</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2386,6 +2461,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128739718</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2509,6 +2589,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740217</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2632,6 +2717,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740970</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2755,6 +2845,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128741270</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2878,6 +2973,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128719243</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3002,6 +3102,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740649</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3121,6 +3226,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128875352</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3248,6 +3358,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128742585</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3368,6 +3483,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128719414</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3492,6 +3612,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740310</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3611,6 +3736,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740350</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3730,8 +3860,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740523</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>